--- a/cards.xlsx
+++ b/cards.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="41">
   <si>
     <t>CardName</t>
   </si>
@@ -105,12 +105,6 @@
   </si>
   <si>
     <t>cupcaces_9.jpg</t>
-  </si>
-  <si>
-    <t>Каки</t>
-  </si>
-  <si>
-    <t>Не вкусно :(</t>
   </si>
   <si>
     <t>InstaImage</t>
@@ -162,7 +156,6 @@
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -188,7 +181,7 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -415,7 +408,7 @@
     <col customWidth="1" min="2" max="2" width="53.57"/>
     <col customWidth="1" min="3" max="3" width="32.14"/>
     <col customWidth="1" min="4" max="4" width="37.14"/>
-    <col customWidth="1" min="5" max="26" width="8.71"/>
+    <col customWidth="1" min="5" max="21" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -719,18 +712,10 @@
       <c r="U10" s="2"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -1728,12 +1713,12 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="41.43"/>
-    <col customWidth="1" min="2" max="26" width="8.71"/>
+    <col customWidth="1" min="2" max="6" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1743,7 +1728,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1753,7 +1738,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1763,7 +1748,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1773,7 +1758,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1783,7 +1768,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1793,7 +1778,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -1803,7 +1788,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1813,7 +1798,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -1823,7 +1808,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
